--- a/Hoàng/2025/T4/CÔNG TY TNHH TK ELEVATOR VIỆT NAM (55-2025)/Bảng kê chi tiết - TK ELEVATOR 2025.xlsx
+++ b/Hoàng/2025/T4/CÔNG TY TNHH TK ELEVATOR VIỆT NAM (55-2025)/Bảng kê chi tiết - TK ELEVATOR 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\DATA-TN\Hoàng\2025\T4\CÔNG TY TNHH TK ELEVATOR VIỆT NAM (55-2025)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9200D49D-FAF7-405D-AF28-DE65D70C0033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2F94FEE-CA5B-4855-8059-8C02A0C5FF8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -354,26 +354,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -699,59 +699,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:32">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="18" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="18" t="s">
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17"/>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="12"/>
+      <c r="AC1" s="12"/>
+      <c r="AD1" s="12"/>
+      <c r="AE1" s="12"/>
       <c r="AF1" s="3"/>
     </row>
     <row r="2" spans="1:32" ht="71.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="17" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
@@ -832,16 +832,16 @@
       <c r="AE2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AF2" s="12" t="s">
+      <c r="AF2" s="14" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:32" s="1" customFormat="1" ht="28.5">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
       <c r="F3" s="4">
         <v>20000</v>
       </c>
@@ -920,7 +920,7 @@
       <c r="AE3" s="4">
         <v>100000</v>
       </c>
-      <c r="AF3" s="12"/>
+      <c r="AF3" s="14"/>
     </row>
     <row r="4" spans="1:32" ht="30">
       <c r="A4" s="5">
@@ -1017,7 +1017,7 @@
         <v>37</v>
       </c>
       <c r="AF4" s="9">
-        <f>SUMIF(F4:AE4,"X",$F$3:$AE$3)</f>
+        <f t="shared" ref="AF4:AF10" si="0">SUMIF(F4:AE4,"X",$F$3:$AE$3)</f>
         <v>1642000</v>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
         <v>37</v>
       </c>
       <c r="AF5" s="9">
-        <f>SUMIF(F5:AE5,"X",$F$3:$AE$3)</f>
+        <f t="shared" si="0"/>
         <v>1642000</v>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
         <v>37</v>
       </c>
       <c r="AF6" s="9">
-        <f>SUMIF(F6:AE6,"X",$F$3:$AE$3)</f>
+        <f t="shared" si="0"/>
         <v>1642000</v>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
         <v>37</v>
       </c>
       <c r="AF7" s="9">
-        <f>SUMIF(F7:AE7,"X",$F$3:$AE$3)</f>
+        <f t="shared" si="0"/>
         <v>1642000</v>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
         <v>37</v>
       </c>
       <c r="AF8" s="9">
-        <f>SUMIF(F8:AE8,"X",$F$3:$AE$3)</f>
+        <f t="shared" si="0"/>
         <v>1642000</v>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
         <v>37</v>
       </c>
       <c r="AF9" s="9">
-        <f>SUMIF(F9:AE9,"X",$F$3:$AE$3)</f>
+        <f t="shared" si="0"/>
         <v>1642000</v>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
         <v>37</v>
       </c>
       <c r="AF10" s="9">
-        <f>SUMIF(F10:AE10,"X",$F$3:$AE$3)</f>
+        <f t="shared" si="0"/>
         <v>1642000</v>
       </c>
     </row>
